--- a/docs/evidence/phase2f/exports/planilla-completa.xlsx
+++ b/docs/evidence/phase2f/exports/planilla-completa.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="254">
   <si>
     <t>ContaLivre — Estados contables (exportación formal)</t>
   </si>
@@ -204,294 +204,282 @@
     <t>Total del activo</t>
   </si>
   <si>
-    <t xml:space="preserve">  Activo corriente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    RC.1.01 RC Caja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    RC.1.02 RC Banco cuenta en dólares</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    RC.1.03 RC Inversiones transitorias</t>
+    <t>Pasivo corriente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  RC.2.01 RC Proveedores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  RC.2.02 RC Préstamos bancarios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  RC.2.03 RC Remuneraciones a pagar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  RC.2.04 RC Impuesto a las ganancias a pagar</t>
+  </si>
+  <si>
+    <t>Pasivo no corriente</t>
+  </si>
+  <si>
+    <t>Total del pasivo</t>
+  </si>
+  <si>
+    <t>Patrimonio neto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  3.3.01 Resultados no asignados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  RC.3.01 RC Capital social</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  RC.3.02 RC Ajuste del capital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  RC.3.03 RC Reserva legal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  RC.3.04 RC Resultados no asignados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Resultado del ejercicio (pendiente de refundición)</t>
+  </si>
+  <si>
+    <t>Total pasivo + patrimonio neto</t>
+  </si>
+  <si>
+    <t>Ingresos por ventas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  RC.4.01 RC Ventas</t>
+  </si>
+  <si>
+    <t>Costo de ventas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  RC.5.01 RC Costo de mercaderías vendidas</t>
+  </si>
+  <si>
+    <t>Resultado bruto</t>
+  </si>
+  <si>
+    <t>Gastos de administración</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  RC.5.02 RC Sueldos y cargas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  RC.5.03 RC Quebrantos por incobrabilidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  RC.5.04 RC Depreciación bienes de uso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  RC.5.05 RC Alquileres</t>
+  </si>
+  <si>
+    <t>Gastos de comercialización</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  RC.5.06 RC Publicidad</t>
+  </si>
+  <si>
+    <t>Resultado operativo</t>
+  </si>
+  <si>
+    <t>Resultados financieros y por tenencia (incl. RECPAM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  RC.4.02 RC Diferencias de cambio ganadas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  RC.5.07 RC Intereses perdidos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  RC.5.08 RC RECPAM</t>
+  </si>
+  <si>
+    <t>Otros ingresos y egresos</t>
+  </si>
+  <si>
+    <t>Resultado antes del impuesto a las ganancias</t>
+  </si>
+  <si>
+    <t>Impuesto a las ganancias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  RC.5.09 RC Impuesto a las ganancias</t>
+  </si>
+  <si>
+    <t>Resultado de operaciones que continúan</t>
+  </si>
+  <si>
+    <t>Resultado del ejercicio</t>
+  </si>
+  <si>
+    <t>Aportes de los propietarios</t>
+  </si>
+  <si>
+    <t>Ganancias reservadas</t>
+  </si>
+  <si>
+    <t>Resultados no asignados</t>
+  </si>
+  <si>
+    <t>Movimiento</t>
+  </si>
+  <si>
+    <t>Capital social</t>
+  </si>
+  <si>
+    <t>Ajuste del capital</t>
+  </si>
+  <si>
+    <t>Reserva legal</t>
+  </si>
+  <si>
+    <t>Resultados de ejercicios anteriores</t>
+  </si>
+  <si>
+    <t>Total PN</t>
+  </si>
+  <si>
+    <t>Total ej. anterior</t>
+  </si>
+  <si>
+    <t>Saldos al inicio</t>
+  </si>
+  <si>
+    <t>Modificaciones de ejercicios anteriores (AREA)</t>
+  </si>
+  <si>
+    <t>Saldo al inicio ajustado</t>
+  </si>
+  <si>
+    <t>Distribuciones de resultados</t>
+  </si>
+  <si>
+    <t>Constitución de reservas</t>
+  </si>
+  <si>
+    <t>Desafectación de reservas</t>
+  </si>
+  <si>
+    <t>Capitalizaciones</t>
+  </si>
+  <si>
+    <t>Otros movimientos del patrimonio</t>
+  </si>
+  <si>
+    <t>Total de variaciones del ejercicio</t>
+  </si>
+  <si>
+    <t>Saldos al cierre</t>
+  </si>
+  <si>
+    <t>Distribuciones</t>
+  </si>
+  <si>
+    <t>Constitución/desafectación de reservas</t>
+  </si>
+  <si>
+    <t>Otros movimientos del PN</t>
+  </si>
+  <si>
+    <t>Importe</t>
+  </si>
+  <si>
+    <t>Efectivo y equivalentes al inicio</t>
+  </si>
+  <si>
+    <t>Actividades operativas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Cobros de clientes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Intereses y costos financieros pagados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Intereses y rendimientos cobrados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Pagos a proveedores de bienes y servicios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Pagos al personal y cargas sociales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Pagos de gastos de administración y comercialización</t>
+  </si>
+  <si>
+    <t>Actividades de inversión</t>
+  </si>
+  <si>
+    <t>Actividades de financiación</t>
+  </si>
+  <si>
+    <t>Flujos sin clasificación (regularizar)</t>
+  </si>
+  <si>
+    <t>Variación neta del efectivo</t>
+  </si>
+  <si>
+    <t>Efectivo y equivalentes al cierre</t>
+  </si>
+  <si>
+    <t>Actividades operativas (método indirecto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Resultado del ejercicio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Partidas devengadas sin efecto en el efectivo (depreciaciones, altas no monetarias, etc.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    RC.1.07 RC Rodados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    RC.2.02 RC Préstamos bancarios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    RC.3.02 RC Ajuste del capital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    RC.3.04 RC Resultados no asignados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    RC.1.08 RC Amortización acumulada rodados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    RC.3.03 RC Reserva legal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Variación de créditos, inventarios y otros activos operativos</t>
   </si>
   <si>
     <t xml:space="preserve">    RC.1.04 RC Deudores por ventas</t>
   </si>
   <si>
+    <t xml:space="preserve">    RC.1.06 RC Mercaderías</t>
+  </si>
+  <si>
     <t xml:space="preserve">    RC.1.05 RC Previsión para incobrables</t>
   </si>
   <si>
-    <t xml:space="preserve">    RC.1.06 RC Mercaderías</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Activo no corriente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    RC.1.07 RC Rodados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    RC.1.08 RC Amortización acumulada rodados</t>
-  </si>
-  <si>
-    <t>Pasivo corriente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  RC.2.01 RC Proveedores</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  RC.2.02 RC Préstamos bancarios</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  RC.2.03 RC Remuneraciones a pagar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  RC.2.04 RC Impuesto a las ganancias a pagar</t>
-  </si>
-  <si>
-    <t>Pasivo no corriente</t>
-  </si>
-  <si>
-    <t>Total del pasivo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Pasivo corriente</t>
+    <t xml:space="preserve">  Variación de proveedores y otros pasivos operativos</t>
   </si>
   <si>
     <t xml:space="preserve">    RC.2.01 RC Proveedores</t>
   </si>
   <si>
-    <t xml:space="preserve">    RC.2.02 RC Préstamos bancarios</t>
-  </si>
-  <si>
     <t xml:space="preserve">    RC.2.03 RC Remuneraciones a pagar</t>
   </si>
   <si>
     <t xml:space="preserve">    RC.2.04 RC Impuesto a las ganancias a pagar</t>
   </si>
   <si>
-    <t xml:space="preserve">  Pasivo no corriente</t>
-  </si>
-  <si>
-    <t>Patrimonio neto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  3.3.01 Resultados no asignados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  RC.3.01 RC Capital social</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  RC.3.02 RC Ajuste del capital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  RC.3.03 RC Reserva legal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  RC.3.04 RC Resultados no asignados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Resultado del ejercicio (pendiente de refundición)</t>
-  </si>
-  <si>
-    <t>Total pasivo + patrimonio neto</t>
-  </si>
-  <si>
-    <t>Ingresos por ventas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  RC.4.01 RC Ventas</t>
-  </si>
-  <si>
-    <t>Costo de ventas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  RC.5.01 RC Costo de mercaderías vendidas</t>
-  </si>
-  <si>
-    <t>Resultado bruto</t>
-  </si>
-  <si>
-    <t>Gastos de administración</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  RC.5.02 RC Sueldos y cargas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  RC.5.03 RC Quebrantos por incobrabilidad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  RC.5.04 RC Depreciación bienes de uso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  RC.5.05 RC Alquileres</t>
-  </si>
-  <si>
-    <t>Gastos de comercialización</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  RC.5.06 RC Publicidad</t>
-  </si>
-  <si>
-    <t>Resultado operativo</t>
-  </si>
-  <si>
-    <t>Resultados financieros y por tenencia (incl. RECPAM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  RC.4.02 RC Diferencias de cambio ganadas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  RC.5.07 RC Intereses perdidos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  RC.5.08 RC RECPAM</t>
-  </si>
-  <si>
-    <t>Otros ingresos y egresos</t>
-  </si>
-  <si>
-    <t>Resultado antes del impuesto a las ganancias</t>
-  </si>
-  <si>
-    <t>Impuesto a las ganancias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  RC.5.09 RC Impuesto a las ganancias</t>
-  </si>
-  <si>
-    <t>Resultado de operaciones que continúan</t>
-  </si>
-  <si>
-    <t>Resultado del ejercicio</t>
-  </si>
-  <si>
-    <t>Aportes de los propietarios</t>
-  </si>
-  <si>
-    <t>Ganancias reservadas</t>
-  </si>
-  <si>
-    <t>Resultados no asignados</t>
-  </si>
-  <si>
-    <t>Movimiento</t>
-  </si>
-  <si>
-    <t>Capital social</t>
-  </si>
-  <si>
-    <t>Ajuste del capital</t>
-  </si>
-  <si>
-    <t>Reserva legal</t>
-  </si>
-  <si>
-    <t>Resultados de ejercicios anteriores</t>
-  </si>
-  <si>
-    <t>Total PN</t>
-  </si>
-  <si>
-    <t>Total ej. anterior</t>
-  </si>
-  <si>
-    <t>Saldos al inicio</t>
-  </si>
-  <si>
-    <t>Distribuciones de resultados</t>
-  </si>
-  <si>
-    <t>Constitución de reservas</t>
-  </si>
-  <si>
-    <t>Desafectación de reservas</t>
-  </si>
-  <si>
-    <t>Capitalizaciones</t>
-  </si>
-  <si>
-    <t>Total de variaciones del ejercicio</t>
-  </si>
-  <si>
-    <t>Saldos al cierre</t>
-  </si>
-  <si>
-    <t>Distribuciones</t>
-  </si>
-  <si>
-    <t>Constitución/desafectación de reservas</t>
-  </si>
-  <si>
-    <t>Otros movimientos del PN</t>
-  </si>
-  <si>
-    <t>Importe</t>
-  </si>
-  <si>
-    <t>Efectivo y equivalentes al inicio</t>
-  </si>
-  <si>
-    <t>Actividades operativas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Cobros de clientes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Intereses y costos financieros pagados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Intereses y rendimientos cobrados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Pagos a proveedores de bienes y servicios</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Pagos al personal y cargas sociales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Pagos de gastos de administración y comercialización</t>
-  </si>
-  <si>
-    <t>Actividades de inversión</t>
-  </si>
-  <si>
-    <t>Actividades de financiación</t>
-  </si>
-  <si>
-    <t>Flujos sin clasificación (regularizar)</t>
-  </si>
-  <si>
-    <t>Variación neta del efectivo</t>
-  </si>
-  <si>
-    <t>Efectivo y equivalentes al cierre</t>
-  </si>
-  <si>
-    <t>Actividades operativas (método indirecto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Resultado del ejercicio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Partidas devengadas sin efecto en el efectivo (depreciaciones, altas no monetarias, etc.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    RC.3.02 RC Ajuste del capital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    RC.3.04 RC Resultados no asignados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    RC.3.03 RC Reserva legal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Variación de créditos, inventarios y otros activos operativos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Variación de proveedores y otros pasivos operativos</t>
-  </si>
-  <si>
     <t>Nota</t>
   </si>
   <si>
@@ -648,6 +636,15 @@
     <t>Nota 18 — Operaciones con partes relacionadas</t>
   </si>
   <si>
+    <t>Nota 19 — Compromisos asumidos</t>
+  </si>
+  <si>
+    <t>Nota 20 — Políticas contables adicionales</t>
+  </si>
+  <si>
+    <t>Nota 21 — Otra información complementaria</t>
+  </si>
+  <si>
     <t>Cuenta</t>
   </si>
   <si>
@@ -684,7 +681,7 @@
     <t>Existencia inicial</t>
   </si>
   <si>
-    <t>Compras y costos incorporables</t>
+    <t>Compras</t>
   </si>
   <si>
     <t>Bienes disponibles para la venta</t>
@@ -699,10 +696,10 @@
     <t>Costo de ventas según ER</t>
   </si>
   <si>
-    <t>CMV: bienes disponibles = EI + compras y costos incorporables</t>
-  </si>
-  <si>
-    <t>CMV: disponibles − existencia final = CMV del puente</t>
+    <t>CMV: bienes disponibles = EI + compras − devoluciones + adquisición + otros</t>
+  </si>
+  <si>
+    <t>CMV: disponibles − existencia final − bajas anormales = CMV del puente</t>
   </si>
   <si>
     <t>CMV del puente = CMV del Estado de Resultados</t>
@@ -759,7 +756,19 @@
     <t>Cotización</t>
   </si>
   <si>
-    <t>Medición</t>
+    <t>Fuente</t>
+  </si>
+  <si>
+    <t>Fecha</t>
+  </si>
+  <si>
+    <t>Tipo cotiz.</t>
+  </si>
+  <si>
+    <t>Medición (Diario)</t>
+  </si>
+  <si>
+    <t>Diferencia</t>
   </si>
   <si>
     <t>USD</t>
@@ -774,7 +783,7 @@
     <t>Información insuficiente</t>
   </si>
   <si>
-    <t>Cantidades y cotizaciones por cuenta: información insuficiente (sin datos estructurados). La medición contable corresponde al saldo del libro en moneda de curso legal. No se utiliza una cotización automática sin identificación de fuente y fecha.</t>
+    <t>Cantidades y cotizaciones por cuenta: información insuficiente (sin detalle operativo cargado). La medición corresponde al saldo del libro en moneda de curso legal. No se utiliza una cotización automática sin identificación de fuente y fecha.</t>
   </si>
 </sst>
 </file>
@@ -1478,15 +1487,15 @@
         <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B2">
         <v>150000</v>
@@ -1497,7 +1506,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B3">
         <v>500000</v>
@@ -1508,7 +1517,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B4">
         <v>650000</v>
@@ -1519,7 +1528,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B5">
         <v>200000</v>
@@ -1530,7 +1539,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B6">
         <v>450000</v>
@@ -1541,7 +1550,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B7">
         <v>450000</v>
@@ -1552,7 +1561,7 @@
         <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C8" t="s">
         <v>28</v>
@@ -1563,7 +1572,7 @@
         <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C9" t="s">
         <v>28</v>
@@ -1574,7 +1583,7 @@
         <v>26</v>
       </c>
       <c r="B10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C10" t="s">
         <v>28</v>
@@ -1585,7 +1594,7 @@
         <v>26</v>
       </c>
       <c r="B11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C11" t="s">
         <v>28</v>
@@ -1604,42 +1613,42 @@
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1674,7 +1683,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1715,64 +1724,88 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D2" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="E2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F2" t="s">
-        <v>249</v>
-      </c>
-      <c r="G2">
+        <v>252</v>
+      </c>
+      <c r="G2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2">
         <v>150000</v>
       </c>
-      <c r="H2">
+      <c r="K2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
   </sheetData>
@@ -1783,7 +1816,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1905,10 +1938,10 @@
         <v>60</v>
       </c>
       <c r="B13">
-        <v>1926000</v>
+        <v>606000</v>
       </c>
       <c r="C13">
-        <v>1330000</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -1916,10 +1949,7 @@
         <v>61</v>
       </c>
       <c r="B14">
-        <v>1206000</v>
-      </c>
-      <c r="C14">
-        <v>1180000</v>
+        <v>220000</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -1927,7 +1957,7 @@
         <v>62</v>
       </c>
       <c r="B15">
-        <v>150000</v>
+        <v>240000</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -1935,7 +1965,7 @@
         <v>63</v>
       </c>
       <c r="B16">
-        <v>100000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -1943,7 +1973,10 @@
         <v>64</v>
       </c>
       <c r="B17">
-        <v>300000</v>
+        <v>96000</v>
+      </c>
+      <c r="C17">
+        <v>66000</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -1951,7 +1984,10 @@
         <v>65</v>
       </c>
       <c r="B18">
-        <v>-30000</v>
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -1959,10 +1995,10 @@
         <v>66</v>
       </c>
       <c r="B19">
-        <v>200000</v>
+        <v>606000</v>
       </c>
       <c r="C19">
-        <v>150000</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -1970,10 +2006,10 @@
         <v>67</v>
       </c>
       <c r="B20">
-        <v>216000</v>
+        <v>1536000</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>1264000</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -1981,7 +2017,10 @@
         <v>68</v>
       </c>
       <c r="B21">
-        <v>240000</v>
+        <v>264000</v>
+      </c>
+      <c r="C21">
+        <v>264000</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -1989,7 +2028,10 @@
         <v>69</v>
       </c>
       <c r="B22">
-        <v>-24000</v>
+        <v>1300000</v>
+      </c>
+      <c r="C22">
+        <v>1000000</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1997,10 +2039,7 @@
         <v>70</v>
       </c>
       <c r="B23">
-        <v>606000</v>
-      </c>
-      <c r="C23">
-        <v>66000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -2008,7 +2047,7 @@
         <v>71</v>
       </c>
       <c r="B24">
-        <v>220000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -2016,7 +2055,7 @@
         <v>72</v>
       </c>
       <c r="B25">
-        <v>240000</v>
+        <v>-160000</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -2024,7 +2063,7 @@
         <v>73</v>
       </c>
       <c r="B26">
-        <v>50000</v>
+        <v>32000</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -2032,164 +2071,9 @@
         <v>74</v>
       </c>
       <c r="B27">
-        <v>96000</v>
+        <v>2142000</v>
       </c>
       <c r="C27">
-        <v>66000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>75</v>
-      </c>
-      <c r="B28">
-        <v>0</v>
-      </c>
-      <c r="C28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>76</v>
-      </c>
-      <c r="B29">
-        <v>606000</v>
-      </c>
-      <c r="C29">
-        <v>66000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>77</v>
-      </c>
-      <c r="B30">
-        <v>606000</v>
-      </c>
-      <c r="C30">
-        <v>66000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>78</v>
-      </c>
-      <c r="B31">
-        <v>220000</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>79</v>
-      </c>
-      <c r="B32">
-        <v>240000</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>80</v>
-      </c>
-      <c r="B33">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>81</v>
-      </c>
-      <c r="B34">
-        <v>96000</v>
-      </c>
-      <c r="C34">
-        <v>66000</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>82</v>
-      </c>
-      <c r="B35">
-        <v>0</v>
-      </c>
-      <c r="C35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>83</v>
-      </c>
-      <c r="B36">
-        <v>1536000</v>
-      </c>
-      <c r="C36">
-        <v>1264000</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>84</v>
-      </c>
-      <c r="B37">
-        <v>264000</v>
-      </c>
-      <c r="C37">
-        <v>264000</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>85</v>
-      </c>
-      <c r="B38">
-        <v>1300000</v>
-      </c>
-      <c r="C38">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>86</v>
-      </c>
-      <c r="B39">
-        <v>90000</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>87</v>
-      </c>
-      <c r="B40">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>88</v>
-      </c>
-      <c r="B41">
-        <v>-160000</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>89</v>
-      </c>
-      <c r="B42">
-        <v>32000</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>90</v>
-      </c>
-      <c r="B43">
-        <v>2142000</v>
-      </c>
-      <c r="C43">
         <v>1330000</v>
       </c>
     </row>
@@ -2217,7 +2101,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B2">
         <v>900000</v>
@@ -2228,7 +2112,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B3">
         <v>900000</v>
@@ -2239,7 +2123,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="B4">
         <v>450000</v>
@@ -2250,7 +2134,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="B5">
         <v>450000</v>
@@ -2261,7 +2145,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="B6">
         <v>450000</v>
@@ -2272,7 +2156,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="B7">
         <v>294000</v>
@@ -2283,7 +2167,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="B8">
         <v>150000</v>
@@ -2294,7 +2178,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="B9">
         <v>30000</v>
@@ -2302,7 +2186,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="B10">
         <v>24000</v>
@@ -2310,7 +2194,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="B11">
         <v>90000</v>
@@ -2318,7 +2202,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="B12">
         <v>60000</v>
@@ -2329,7 +2213,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="B13">
         <v>60000</v>
@@ -2337,7 +2221,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="B14">
         <v>96000</v>
@@ -2348,7 +2232,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="B15">
         <v>-34000</v>
@@ -2359,7 +2243,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="B16">
         <v>30000</v>
@@ -2367,7 +2251,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="B17">
         <v>-24000</v>
@@ -2375,7 +2259,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="B18">
         <v>-40000</v>
@@ -2383,7 +2267,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2394,7 +2278,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="B20">
         <v>62000</v>
@@ -2405,7 +2289,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B21">
         <v>30000</v>
@@ -2416,7 +2300,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="B22">
         <v>30000</v>
@@ -2427,7 +2311,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="B23">
         <v>32000</v>
@@ -2438,7 +2322,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="B24">
         <v>32000</v>
@@ -2455,7 +2339,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -2463,19 +2347,19 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>28</v>
@@ -2486,33 +2370,33 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B2" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="C2" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="D2" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="E2" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="F2" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="G2" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="H2" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="B3">
         <v>1000000</v>
@@ -2529,66 +2413,60 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B4">
-        <v>300000</v>
-      </c>
-      <c r="C4">
-        <v>40000</v>
+        <v>109</v>
+      </c>
+      <c r="E4">
+        <v>-20000</v>
       </c>
       <c r="G4">
-        <v>340000</v>
+        <v>-20000</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>125</v>
+        <v>110</v>
+      </c>
+      <c r="B5">
+        <v>1000000</v>
       </c>
       <c r="E5">
-        <v>-100000</v>
+        <v>244000</v>
       </c>
       <c r="G5">
-        <v>-100000</v>
+        <v>1244000</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>126</v>
-      </c>
-      <c r="D6">
-        <v>13200</v>
-      </c>
-      <c r="E6">
-        <v>-13200</v>
+        <v>98</v>
+      </c>
+      <c r="B6">
+        <v>300000</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>127</v>
-      </c>
-      <c r="D7">
-        <v>-3200</v>
+        <v>111</v>
       </c>
       <c r="E7">
-        <v>3200</v>
+        <v>-80000</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>-80000</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>128</v>
-      </c>
-      <c r="C8">
-        <v>50000</v>
+        <v>112</v>
+      </c>
+      <c r="D8">
+        <v>13200</v>
       </c>
       <c r="E8">
-        <v>-50000</v>
+        <v>-13200</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2598,59 +2476,98 @@
       <c r="A9" t="s">
         <v>113</v>
       </c>
-      <c r="F9">
-        <v>32000</v>
+      <c r="D9">
+        <v>-3200</v>
+      </c>
+      <c r="E9">
+        <v>3200</v>
       </c>
       <c r="G9">
-        <v>32000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>129</v>
-      </c>
-      <c r="B10">
-        <v>300000</v>
+        <v>114</v>
       </c>
       <c r="C10">
-        <v>90000</v>
-      </c>
-      <c r="D10">
-        <v>10000</v>
+        <v>50000</v>
       </c>
       <c r="E10">
-        <v>-160000</v>
-      </c>
-      <c r="F10">
-        <v>32000</v>
+        <v>-50000</v>
       </c>
       <c r="G10">
-        <v>272000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>130</v>
-      </c>
-      <c r="B11">
-        <v>1300000</v>
-      </c>
-      <c r="C11">
-        <v>90000</v>
-      </c>
-      <c r="D11">
-        <v>10000</v>
-      </c>
-      <c r="E11">
-        <v>104000</v>
+        <v>97</v>
       </c>
       <c r="F11">
         <v>32000</v>
       </c>
       <c r="G11">
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>115</v>
+      </c>
+      <c r="C12">
+        <v>40000</v>
+      </c>
+      <c r="G12">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>116</v>
+      </c>
+      <c r="B13">
+        <v>300000</v>
+      </c>
+      <c r="C13">
+        <v>90000</v>
+      </c>
+      <c r="D13">
+        <v>10000</v>
+      </c>
+      <c r="E13">
+        <v>-140000</v>
+      </c>
+      <c r="F13">
+        <v>32000</v>
+      </c>
+      <c r="G13">
+        <v>292000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>117</v>
+      </c>
+      <c r="B14">
+        <v>1300000</v>
+      </c>
+      <c r="C14">
+        <v>90000</v>
+      </c>
+      <c r="D14">
+        <v>10000</v>
+      </c>
+      <c r="E14">
+        <v>104000</v>
+      </c>
+      <c r="F14">
+        <v>32000</v>
+      </c>
+      <c r="G14">
         <v>1536000</v>
       </c>
-      <c r="H11">
+      <c r="H14">
         <v>1264000</v>
       </c>
     </row>
@@ -2678,7 +2595,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2686,7 +2603,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="B3">
         <v>1390000</v>
@@ -2694,7 +2611,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="B4">
         <v>160000</v>
@@ -2702,7 +2619,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="B5">
         <v>10000</v>
@@ -2710,7 +2627,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="B6">
         <v>264000</v>
@@ -2718,7 +2635,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="B7">
         <v>32000</v>
@@ -2726,7 +2643,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="B8">
         <v>1536000</v>
@@ -2748,12 +2665,12 @@
         <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="B2">
         <v>1180000</v>
@@ -2761,7 +2678,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="B3">
         <v>56000</v>
@@ -2769,7 +2686,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="B4">
         <v>600000</v>
@@ -2777,7 +2694,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="B5">
         <v>-24000</v>
@@ -2785,7 +2702,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="B6">
         <v>30000</v>
@@ -2793,7 +2710,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="B7">
         <v>-300000</v>
@@ -2801,7 +2718,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="B8">
         <v>-100000</v>
@@ -2809,7 +2726,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="B9">
         <v>-150000</v>
@@ -2817,7 +2734,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="B10">
         <v>-100000</v>
@@ -2833,7 +2750,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="B12">
         <v>220000</v>
@@ -2841,7 +2758,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="B13">
         <v>300000</v>
@@ -2849,7 +2766,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="B14">
         <v>-80000</v>
@@ -2857,7 +2774,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2865,7 +2782,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="B16">
         <v>176000</v>
@@ -2873,7 +2790,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="B17">
         <v>1356000</v>
@@ -2895,12 +2812,12 @@
         <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="B2">
         <v>1180000</v>
@@ -2908,7 +2825,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="B3">
         <v>56000</v>
@@ -2916,7 +2833,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="B4">
         <v>32000</v>
@@ -2924,7 +2841,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="B5">
         <v>44000</v>
@@ -2932,7 +2849,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>68</v>
+        <v>138</v>
       </c>
       <c r="B6">
         <v>-240000</v>
@@ -2940,7 +2857,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="B7">
         <v>240000</v>
@@ -2948,7 +2865,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="B8">
         <v>90000</v>
@@ -2956,7 +2873,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="B9">
         <v>-80000</v>
@@ -2964,7 +2881,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>69</v>
+        <v>142</v>
       </c>
       <c r="B10">
         <v>24000</v>
@@ -2972,7 +2889,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="B11">
         <v>10000</v>
@@ -2980,7 +2897,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="B12">
         <v>-320000</v>
@@ -2988,7 +2905,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>64</v>
+        <v>145</v>
       </c>
       <c r="B13">
         <v>-300000</v>
@@ -2996,7 +2913,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>66</v>
+        <v>146</v>
       </c>
       <c r="B14">
         <v>-50000</v>
@@ -3004,7 +2921,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>65</v>
+        <v>147</v>
       </c>
       <c r="B15">
         <v>30000</v>
@@ -3012,7 +2929,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="B16">
         <v>300000</v>
@@ -3020,7 +2937,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>78</v>
+        <v>149</v>
       </c>
       <c r="B17">
         <v>220000</v>
@@ -3028,7 +2945,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="B18">
         <v>50000</v>
@@ -3036,7 +2953,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>81</v>
+        <v>151</v>
       </c>
       <c r="B19">
         <v>30000</v>
@@ -3044,7 +2961,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="B20">
         <v>-100000</v>
@@ -3060,7 +2977,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="B22">
         <v>220000</v>
@@ -3068,7 +2985,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="B23">
         <v>300000</v>
@@ -3076,7 +2993,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="B24">
         <v>-80000</v>
@@ -3084,7 +3001,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -3092,7 +3009,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="B26">
         <v>176000</v>
@@ -3100,7 +3017,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="B27">
         <v>1356000</v>
@@ -3114,35 +3031,35 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>46</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B2" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C2" t="s">
         <v>28</v>
@@ -3159,10 +3076,10 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C3">
         <v>1356000</v>
@@ -3182,7 +3099,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C4">
         <v>1206000</v>
@@ -3191,7 +3108,7 @@
         <v>1180000</v>
       </c>
       <c r="E4" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F4" t="s">
         <v>28</v>
@@ -3202,7 +3119,7 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C5">
         <v>150000</v>
@@ -3211,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F5" t="s">
         <v>28</v>
@@ -3219,7 +3136,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B6" t="s">
         <v>28</v>
@@ -3242,7 +3159,7 @@
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C7">
         <v>100000</v>
@@ -3251,7 +3168,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F7" t="s">
         <v>28</v>
@@ -3259,10 +3176,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B8" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C8">
         <v>270000</v>
@@ -3282,7 +3199,7 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C9">
         <v>300000</v>
@@ -3291,7 +3208,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F9" t="s">
         <v>28</v>
@@ -3302,7 +3219,7 @@
         <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C10">
         <v>-30000</v>
@@ -3311,7 +3228,7 @@
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F10" t="s">
         <v>28</v>
@@ -3319,7 +3236,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B11" t="s">
         <v>28</v>
@@ -3342,7 +3259,7 @@
         <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C12" t="s">
         <v>28</v>
@@ -3351,7 +3268,7 @@
         <v>28</v>
       </c>
       <c r="E12" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F12" t="s">
         <v>28</v>
@@ -3359,7 +3276,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B13" t="s">
         <v>28</v>
@@ -3382,7 +3299,7 @@
         <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C14">
         <v>200000</v>
@@ -3391,7 +3308,7 @@
         <v>150000</v>
       </c>
       <c r="E14" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F14" t="s">
         <v>28</v>
@@ -3399,10 +3316,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B15" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C15">
         <v>216000</v>
@@ -3422,7 +3339,7 @@
         <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C16">
         <v>240000</v>
@@ -3431,7 +3348,7 @@
         <v>28</v>
       </c>
       <c r="E16" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F16" t="s">
         <v>28</v>
@@ -3442,7 +3359,7 @@
         <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C17">
         <v>-24000</v>
@@ -3451,7 +3368,7 @@
         <v>28</v>
       </c>
       <c r="E17" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F17" t="s">
         <v>28</v>
@@ -3459,7 +3376,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B18" t="s">
         <v>28</v>
@@ -3482,7 +3399,7 @@
         <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C19" t="s">
         <v>28</v>
@@ -3491,7 +3408,7 @@
         <v>28</v>
       </c>
       <c r="E19" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F19" t="s">
         <v>28</v>
@@ -3499,7 +3416,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B20" t="s">
         <v>28</v>
@@ -3522,7 +3439,7 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C21">
         <v>220000</v>
@@ -3531,7 +3448,7 @@
         <v>0</v>
       </c>
       <c r="E21" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F21" t="s">
         <v>28</v>
@@ -3539,7 +3456,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B22" t="s">
         <v>28</v>
@@ -3562,7 +3479,7 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C23">
         <v>240000</v>
@@ -3571,7 +3488,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F23" t="s">
         <v>28</v>
@@ -3579,7 +3496,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B24" t="s">
         <v>28</v>
@@ -3602,7 +3519,7 @@
         <v>28</v>
       </c>
       <c r="B25" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C25">
         <v>50000</v>
@@ -3611,7 +3528,7 @@
         <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F25" t="s">
         <v>28</v>
@@ -3619,7 +3536,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B26" t="s">
         <v>28</v>
@@ -3642,7 +3559,7 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C27">
         <v>96000</v>
@@ -3651,7 +3568,7 @@
         <v>66000</v>
       </c>
       <c r="E27" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F27" t="s">
         <v>28</v>
@@ -3659,7 +3576,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B28" t="s">
         <v>28</v>
@@ -3682,7 +3599,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C29" t="s">
         <v>28</v>
@@ -3691,7 +3608,7 @@
         <v>28</v>
       </c>
       <c r="E29" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F29" t="s">
         <v>28</v>
@@ -3699,7 +3616,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B30" t="s">
         <v>28</v>
@@ -3722,7 +3639,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C31">
         <v>264000</v>
@@ -3731,7 +3648,7 @@
         <v>264000</v>
       </c>
       <c r="E31" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F31" t="s">
         <v>28</v>
@@ -3742,7 +3659,7 @@
         <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C32">
         <v>1300000</v>
@@ -3751,7 +3668,7 @@
         <v>1000000</v>
       </c>
       <c r="E32" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F32" t="s">
         <v>28</v>
@@ -3762,7 +3679,7 @@
         <v>28</v>
       </c>
       <c r="B33" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C33">
         <v>90000</v>
@@ -3771,7 +3688,7 @@
         <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F33" t="s">
         <v>28</v>
@@ -3782,7 +3699,7 @@
         <v>28</v>
       </c>
       <c r="B34" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C34">
         <v>10000</v>
@@ -3791,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="E34" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F34" t="s">
         <v>28</v>
@@ -3802,7 +3719,7 @@
         <v>28</v>
       </c>
       <c r="B35" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C35">
         <v>-160000</v>
@@ -3811,7 +3728,7 @@
         <v>0</v>
       </c>
       <c r="E35" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F35" t="s">
         <v>28</v>
@@ -3819,10 +3736,10 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B36" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C36">
         <v>-34000</v>
@@ -3842,7 +3759,7 @@
         <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C37">
         <v>30000</v>
@@ -3851,7 +3768,7 @@
         <v>28</v>
       </c>
       <c r="E37" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F37" t="s">
         <v>28</v>
@@ -3862,7 +3779,7 @@
         <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C38">
         <v>-24000</v>
@@ -3871,7 +3788,7 @@
         <v>28</v>
       </c>
       <c r="E38" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F38" t="s">
         <v>28</v>
@@ -3882,7 +3799,7 @@
         <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C39">
         <v>-40000</v>
@@ -3891,7 +3808,7 @@
         <v>28</v>
       </c>
       <c r="E39" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F39" t="s">
         <v>28</v>
@@ -3899,10 +3816,10 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B40" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C40" t="s">
         <v>28</v>
@@ -3922,7 +3839,7 @@
         <v>28</v>
       </c>
       <c r="B41" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C41" t="s">
         <v>28</v>
@@ -3931,7 +3848,7 @@
         <v>28</v>
       </c>
       <c r="E41" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F41" t="s">
         <v>28</v>
@@ -3939,10 +3856,10 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B42" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C42" t="s">
         <v>28</v>
@@ -3962,7 +3879,7 @@
         <v>28</v>
       </c>
       <c r="B43" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C43" t="s">
         <v>28</v>
@@ -3971,7 +3888,7 @@
         <v>28</v>
       </c>
       <c r="E43" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F43" t="s">
         <v>28</v>
@@ -3979,10 +3896,10 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B44" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C44" t="s">
         <v>28</v>
@@ -4002,18 +3919,138 @@
         <v>28</v>
       </c>
       <c r="B45" t="s">
+        <v>200</v>
+      </c>
+      <c r="C45" t="s">
+        <v>28</v>
+      </c>
+      <c r="D45" t="s">
+        <v>28</v>
+      </c>
+      <c r="E45" t="s">
+        <v>201</v>
+      </c>
+      <c r="F45" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>204</v>
       </c>
-      <c r="C45" t="s">
-        <v>28</v>
-      </c>
-      <c r="D45" t="s">
-        <v>28</v>
-      </c>
-      <c r="E45" t="s">
+      <c r="B46" t="s">
+        <v>199</v>
+      </c>
+      <c r="C46" t="s">
+        <v>28</v>
+      </c>
+      <c r="D46" t="s">
+        <v>28</v>
+      </c>
+      <c r="E46" t="s">
+        <v>28</v>
+      </c>
+      <c r="F46" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>28</v>
+      </c>
+      <c r="B47" t="s">
+        <v>200</v>
+      </c>
+      <c r="C47" t="s">
+        <v>28</v>
+      </c>
+      <c r="D47" t="s">
+        <v>28</v>
+      </c>
+      <c r="E47" t="s">
+        <v>201</v>
+      </c>
+      <c r="F47" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>205</v>
       </c>
-      <c r="F45" t="s">
+      <c r="B48" t="s">
+        <v>199</v>
+      </c>
+      <c r="C48" t="s">
+        <v>28</v>
+      </c>
+      <c r="D48" t="s">
+        <v>28</v>
+      </c>
+      <c r="E48" t="s">
+        <v>28</v>
+      </c>
+      <c r="F48" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>28</v>
+      </c>
+      <c r="B49" t="s">
+        <v>200</v>
+      </c>
+      <c r="C49" t="s">
+        <v>28</v>
+      </c>
+      <c r="D49" t="s">
+        <v>28</v>
+      </c>
+      <c r="E49" t="s">
+        <v>201</v>
+      </c>
+      <c r="F49" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>206</v>
+      </c>
+      <c r="B50" t="s">
+        <v>199</v>
+      </c>
+      <c r="C50" t="s">
+        <v>28</v>
+      </c>
+      <c r="D50" t="s">
+        <v>28</v>
+      </c>
+      <c r="E50" t="s">
+        <v>28</v>
+      </c>
+      <c r="F50" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>28</v>
+      </c>
+      <c r="B51" t="s">
+        <v>200</v>
+      </c>
+      <c r="C51" t="s">
+        <v>28</v>
+      </c>
+      <c r="D51" t="s">
+        <v>28</v>
+      </c>
+      <c r="E51" t="s">
+        <v>201</v>
+      </c>
+      <c r="F51" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4030,27 +4067,27 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B2">
         <v>150000</v>
@@ -4064,7 +4101,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B3">
         <v>30000</v>
@@ -4078,7 +4115,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B4">
         <v>24000</v>
@@ -4092,7 +4129,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B5">
         <v>90000</v>
@@ -4109,7 +4146,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B6">
         <v>60000</v>
@@ -4123,7 +4160,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B7">
         <v>24000</v>
@@ -4137,7 +4174,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B8">
         <v>40000</v>
@@ -4151,7 +4188,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B9">
         <v>418000</v>

--- a/docs/evidence/phase2f/exports/planilla-completa.xlsx
+++ b/docs/evidence/phase2f/exports/planilla-completa.xlsx
@@ -11,18 +11,19 @@
     <sheet sheetId="5" name="EEPN resumen" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="EFE directo" state="visible" r:id="rId9"/>
     <sheet sheetId="7" name="EFE indirecto" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="Notas" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="Gastos por función" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="Costo de ventas" state="visible" r:id="rId13"/>
-    <sheet sheetId="11" name="Bienes de uso" state="visible" r:id="rId14"/>
-    <sheet sheetId="12" name="Moneda extranjera" state="visible" r:id="rId15"/>
+    <sheet sheetId="8" name="EFE no monetarias" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="Notas" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="Gastos por función" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="Costo de ventas" state="visible" r:id="rId14"/>
+    <sheet sheetId="12" name="Bienes de uso" state="visible" r:id="rId15"/>
+    <sheet sheetId="13" name="Moneda extranjera" state="visible" r:id="rId16"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="257">
   <si>
     <t>ContaLivre — Estados contables (exportación formal)</t>
   </si>
@@ -84,7 +85,7 @@
     <t>Motor contable</t>
   </si>
   <si>
-    <t>2F.0</t>
+    <t>2G.0</t>
   </si>
   <si>
     <t>Versión de reporte</t>
@@ -150,7 +151,7 @@
     <t>Anexo de bienes de uso: valor residual = Bienes de uso netos del ESP</t>
   </si>
   <si>
-    <t>EFE: variación neta = efectivo final − inicial</t>
+    <t>EFE: variación neta = efectivo final − inicial modificado</t>
   </si>
   <si>
     <t>Efectivo final del EFE = Caja y equivalentes del ESP</t>
@@ -162,6 +163,9 @@
     <t>EFE: sin flujos materiales pendientes de clasificación</t>
   </si>
   <si>
+    <t>EFE: disposiciones de activos resueltas (sin ventas a crédito/mixtas sin clasificar)</t>
+  </si>
+  <si>
     <t>Concepto</t>
   </si>
   <si>
@@ -387,97 +391,103 @@
     <t>Otros movimientos del PN</t>
   </si>
   <si>
+    <t>Efectivo y equivalentes al inicio</t>
+  </si>
+  <si>
+    <t>Actividades operativas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Cobros de clientes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Intereses y costos financieros pagados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Intereses y rendimientos cobrados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Pagos a proveedores de bienes y servicios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Pagos al personal y cargas sociales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Pagos de gastos de administración y comercialización</t>
+  </si>
+  <si>
+    <t>Actividades de inversión</t>
+  </si>
+  <si>
+    <t>Actividades de financiación</t>
+  </si>
+  <si>
+    <t>Variación neta del efectivo</t>
+  </si>
+  <si>
+    <t>Efectivo y equivalentes al cierre</t>
+  </si>
+  <si>
+    <t>Actividades operativas (método indirecto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Resultado del ejercicio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Partidas devengadas sin efecto en el efectivo (depreciaciones, altas no monetarias, etc.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    RC.1.07 RC Rodados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    RC.2.02 RC Préstamos bancarios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    RC.3.02 RC Ajuste del capital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    RC.3.04 RC Resultados no asignados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    RC.1.08 RC Amortización acumulada rodados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    RC.3.03 RC Reserva legal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Variación de créditos, inventarios y otros activos operativos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    RC.1.04 RC Deudores por ventas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    RC.1.06 RC Mercaderías</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    RC.1.05 RC Previsión para incobrables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Variación de proveedores y otros pasivos operativos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    RC.2.01 RC Proveedores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    RC.2.03 RC Remuneraciones a pagar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    RC.2.04 RC Impuesto a las ganancias a pagar</t>
+  </si>
+  <si>
+    <t>Operaciones de inversión y financiación que no afectaron el efectivo</t>
+  </si>
+  <si>
     <t>Importe</t>
   </si>
   <si>
-    <t>Efectivo y equivalentes al inicio</t>
-  </si>
-  <si>
-    <t>Actividades operativas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Cobros de clientes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Intereses y costos financieros pagados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Intereses y rendimientos cobrados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Pagos a proveedores de bienes y servicios</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Pagos al personal y cargas sociales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Pagos de gastos de administración y comercialización</t>
-  </si>
-  <si>
-    <t>Actividades de inversión</t>
-  </si>
-  <si>
-    <t>Actividades de financiación</t>
-  </si>
-  <si>
-    <t>Flujos sin clasificación (regularizar)</t>
-  </si>
-  <si>
-    <t>Variación neta del efectivo</t>
-  </si>
-  <si>
-    <t>Efectivo y equivalentes al cierre</t>
-  </si>
-  <si>
-    <t>Actividades operativas (método indirecto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Resultado del ejercicio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Partidas devengadas sin efecto en el efectivo (depreciaciones, altas no monetarias, etc.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    RC.1.07 RC Rodados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    RC.2.02 RC Préstamos bancarios</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    RC.3.02 RC Ajuste del capital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    RC.3.04 RC Resultados no asignados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    RC.1.08 RC Amortización acumulada rodados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    RC.3.03 RC Reserva legal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Variación de créditos, inventarios y otros activos operativos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    RC.1.04 RC Deudores por ventas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    RC.1.06 RC Mercaderías</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    RC.1.05 RC Previsión para incobrables</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Variación de proveedores y otros pasivos operativos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    RC.2.01 RC Proveedores</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    RC.2.03 RC Remuneraciones a pagar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    RC.2.04 RC Impuesto a las ganancias a pagar</t>
+    <t>2025-12-31 — RC Depreciación del rodado</t>
+  </si>
+  <si>
+    <t>2025-12-31 — RC Reexpresión del capital (RECPAM)</t>
   </si>
   <si>
     <t>Nota</t>
@@ -699,7 +709,7 @@
     <t>CMV: bienes disponibles = EI + compras − devoluciones + adquisición + otros</t>
   </si>
   <si>
-    <t>CMV: disponibles − existencia final − bajas anormales = CMV del puente</t>
+    <t>CMV: disponibles − existencia final − bajas anormales − transferencias a producción = CMV del puente</t>
   </si>
   <si>
     <t>CMV del puente = CMV del Estado de Resultados</t>
@@ -1164,7 +1174,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1468,6 +1478,17 @@
         <v>45</v>
       </c>
       <c r="C34" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>26</v>
+      </c>
+      <c r="B35" t="s">
+        <v>46</v>
+      </c>
+      <c r="C35" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1479,125 +1500,148 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>210</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>211</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B2">
         <v>150000</v>
       </c>
       <c r="C2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>150000</v>
+      </c>
+      <c r="F2">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B3">
+        <v>30000</v>
+      </c>
+      <c r="C3">
+        <v>30000</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B4">
+        <v>24000</v>
+      </c>
+      <c r="C4">
+        <v>24000</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>219</v>
       </c>
-      <c r="B3">
-        <v>500000</v>
-      </c>
-      <c r="C3">
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B5">
+        <v>90000</v>
+      </c>
+      <c r="C5">
+        <v>54000</v>
+      </c>
+      <c r="D5">
+        <v>36000</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>220</v>
       </c>
-      <c r="B4">
-        <v>650000</v>
-      </c>
-      <c r="C4">
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>221</v>
-      </c>
-      <c r="B5">
-        <v>200000</v>
-      </c>
-      <c r="C5">
-        <v>150000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>222</v>
-      </c>
       <c r="B6">
-        <v>450000</v>
-      </c>
-      <c r="C6">
-        <v>250000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>60000</v>
+      </c>
+      <c r="D6">
+        <v>60000</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="B7">
-        <v>450000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>24000</v>
+      </c>
+      <c r="E7">
+        <v>24000</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" t="s">
-        <v>224</v>
-      </c>
-      <c r="C8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+      <c r="B8">
+        <v>40000</v>
+      </c>
+      <c r="E8">
+        <v>40000</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" t="s">
-        <v>225</v>
-      </c>
-      <c r="C9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" t="s">
-        <v>226</v>
-      </c>
-      <c r="C10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" t="s">
-        <v>227</v>
-      </c>
-      <c r="C11" t="s">
-        <v>28</v>
+        <v>211</v>
+      </c>
+      <c r="B9">
+        <v>418000</v>
+      </c>
+      <c r="C9">
+        <v>258000</v>
+      </c>
+      <c r="D9">
+        <v>96000</v>
+      </c>
+      <c r="E9">
+        <v>64000</v>
+      </c>
+      <c r="F9">
+        <v>120000</v>
       </c>
     </row>
   </sheetData>
@@ -1608,112 +1652,125 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B2">
+        <v>150000</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B3">
+        <v>500000</v>
+      </c>
+      <c r="C3">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>223</v>
+      </c>
+      <c r="B4">
+        <v>650000</v>
+      </c>
+      <c r="C4">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>224</v>
+      </c>
+      <c r="B5">
+        <v>200000</v>
+      </c>
+      <c r="C5">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>225</v>
+      </c>
+      <c r="B6">
+        <v>450000</v>
+      </c>
+      <c r="C6">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>226</v>
+      </c>
+      <c r="B7">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
+        <v>227</v>
+      </c>
+      <c r="C8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" t="s">
         <v>228</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" t="s">
         <v>229</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" t="s">
         <v>230</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>239</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>240000</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>240000</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>24000</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>24000</v>
-      </c>
-      <c r="J2">
-        <v>216000</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>208</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>240000</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>240000</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>24000</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>24000</v>
-      </c>
-      <c r="J3">
-        <v>216000</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
+      <c r="C11" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1724,42 +1781,158 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>240000</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>240000</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>24000</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>24000</v>
+      </c>
+      <c r="J2">
+        <v>216000</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>240000</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>240000</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>24000</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>24000</v>
+      </c>
+      <c r="J3">
+        <v>216000</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>13</v>
@@ -1767,22 +1940,22 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D2" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="E2" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F2" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G2" t="s">
         <v>28</v>
@@ -1805,7 +1978,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -1821,18 +1994,18 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B2">
         <v>1926000</v>
@@ -1843,7 +2016,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B3">
         <v>1206000</v>
@@ -1854,7 +2027,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B4">
         <v>150000</v>
@@ -1862,7 +2035,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B5">
         <v>100000</v>
@@ -1870,7 +2043,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B6">
         <v>300000</v>
@@ -1878,7 +2051,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B7">
         <v>-30000</v>
@@ -1886,7 +2059,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B8">
         <v>200000</v>
@@ -1897,7 +2070,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B9">
         <v>216000</v>
@@ -1908,7 +2081,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B10">
         <v>240000</v>
@@ -1916,7 +2089,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B11">
         <v>-24000</v>
@@ -1924,7 +2097,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12">
         <v>2142000</v>
@@ -1935,7 +2108,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13">
         <v>606000</v>
@@ -1946,7 +2119,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14">
         <v>220000</v>
@@ -1954,7 +2127,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B15">
         <v>240000</v>
@@ -1962,7 +2135,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B16">
         <v>50000</v>
@@ -1970,7 +2143,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B17">
         <v>96000</v>
@@ -1981,7 +2154,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1992,7 +2165,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B19">
         <v>606000</v>
@@ -2003,7 +2176,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B20">
         <v>1536000</v>
@@ -2014,7 +2187,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B21">
         <v>264000</v>
@@ -2025,7 +2198,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B22">
         <v>1300000</v>
@@ -2036,7 +2209,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B23">
         <v>90000</v>
@@ -2044,7 +2217,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B24">
         <v>10000</v>
@@ -2052,7 +2225,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B25">
         <v>-160000</v>
@@ -2060,7 +2233,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B26">
         <v>32000</v>
@@ -2068,7 +2241,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B27">
         <v>2142000</v>
@@ -2090,18 +2263,18 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B2">
         <v>900000</v>
@@ -2112,7 +2285,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B3">
         <v>900000</v>
@@ -2123,7 +2296,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B4">
         <v>450000</v>
@@ -2134,7 +2307,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B5">
         <v>450000</v>
@@ -2145,7 +2318,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B6">
         <v>450000</v>
@@ -2156,7 +2329,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B7">
         <v>294000</v>
@@ -2167,7 +2340,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B8">
         <v>150000</v>
@@ -2178,7 +2351,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B9">
         <v>30000</v>
@@ -2186,7 +2359,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B10">
         <v>24000</v>
@@ -2194,7 +2367,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B11">
         <v>90000</v>
@@ -2202,7 +2375,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B12">
         <v>60000</v>
@@ -2213,7 +2386,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B13">
         <v>60000</v>
@@ -2221,7 +2394,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B14">
         <v>96000</v>
@@ -2232,7 +2405,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B15">
         <v>-34000</v>
@@ -2243,7 +2416,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B16">
         <v>30000</v>
@@ -2251,7 +2424,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B17">
         <v>-24000</v>
@@ -2259,7 +2432,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B18">
         <v>-40000</v>
@@ -2267,7 +2440,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2278,7 +2451,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B20">
         <v>62000</v>
@@ -2289,7 +2462,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B21">
         <v>30000</v>
@@ -2300,7 +2473,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B22">
         <v>30000</v>
@@ -2311,7 +2484,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B23">
         <v>32000</v>
@@ -2322,7 +2495,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B24">
         <v>32000</v>
@@ -2347,19 +2520,19 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>28</v>
@@ -2370,33 +2543,33 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B3">
         <v>1000000</v>
@@ -2413,7 +2586,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E4">
         <v>-20000</v>
@@ -2424,7 +2597,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B5">
         <v>1000000</v>
@@ -2438,7 +2611,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B6">
         <v>300000</v>
@@ -2449,7 +2622,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E7">
         <v>-80000</v>
@@ -2460,7 +2633,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D8">
         <v>13200</v>
@@ -2474,7 +2647,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D9">
         <v>-3200</v>
@@ -2488,7 +2661,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C10">
         <v>50000</v>
@@ -2502,7 +2675,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F11">
         <v>32000</v>
@@ -2513,7 +2686,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C12">
         <v>40000</v>
@@ -2524,7 +2697,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B13">
         <v>300000</v>
@@ -2547,7 +2720,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B14">
         <v>1300000</v>
@@ -2584,18 +2757,18 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2603,7 +2776,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B3">
         <v>1390000</v>
@@ -2611,7 +2784,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B4">
         <v>160000</v>
@@ -2619,7 +2792,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B5">
         <v>10000</v>
@@ -2627,7 +2800,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B6">
         <v>264000</v>
@@ -2635,7 +2808,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B7">
         <v>32000</v>
@@ -2643,7 +2816,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B8">
         <v>1536000</v>
@@ -2657,34 +2830,43 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>122</v>
       </c>
       <c r="B2">
         <v>1180000</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>123</v>
       </c>
       <c r="B3">
         <v>56000</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C3">
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>124</v>
       </c>
@@ -2692,7 +2874,7 @@
         <v>600000</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>125</v>
       </c>
@@ -2700,7 +2882,7 @@
         <v>-24000</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>126</v>
       </c>
@@ -2708,7 +2890,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>127</v>
       </c>
@@ -2716,7 +2898,7 @@
         <v>-300000</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>128</v>
       </c>
@@ -2724,7 +2906,7 @@
         <v>-100000</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>129</v>
       </c>
@@ -2732,68 +2914,72 @@
         <v>-150000</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>130</v>
       </c>
       <c r="B10">
         <v>-100000</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B11">
         <v>-100000</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>131</v>
       </c>
       <c r="B12">
         <v>220000</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C12">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B13">
         <v>300000</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B14">
         <v>-80000</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>132</v>
       </c>
       <c r="B15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+        <v>176000</v>
+      </c>
+      <c r="C15">
+        <v>1180000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>133</v>
       </c>
       <c r="B16">
-        <v>176000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>134</v>
-      </c>
-      <c r="B17">
         <v>1356000</v>
+      </c>
+      <c r="C16">
+        <v>1180000</v>
       </c>
     </row>
   </sheetData>
@@ -2804,223 +2990,236 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>122</v>
       </c>
       <c r="B2">
         <v>1180000</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B3">
         <v>56000</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C3">
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B4">
         <v>32000</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B5">
+        <v>64000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>137</v>
-      </c>
-      <c r="B5">
-        <v>44000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>138</v>
       </c>
       <c r="B6">
         <v>-240000</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B7">
         <v>240000</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B8">
         <v>90000</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>140</v>
+      </c>
+      <c r="B9">
+        <v>-60000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>141</v>
-      </c>
-      <c r="B9">
-        <v>-80000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>142</v>
       </c>
       <c r="B10">
         <v>24000</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B11">
         <v>10000</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B12">
         <v>-320000</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B13">
         <v>-300000</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B14">
         <v>-50000</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B15">
         <v>30000</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>147</v>
+      </c>
+      <c r="B16">
+        <v>280000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>148</v>
       </c>
-      <c r="B16">
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="B17">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>149</v>
-      </c>
-      <c r="B17">
-        <v>220000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>150</v>
       </c>
       <c r="B18">
         <v>50000</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B19">
         <v>30000</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>130</v>
       </c>
       <c r="B20">
         <v>-100000</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B21">
         <v>-100000</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>131</v>
       </c>
       <c r="B22">
         <v>220000</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C22">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B23">
         <v>300000</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B24">
         <v>-80000</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>132</v>
       </c>
       <c r="B25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+        <v>176000</v>
+      </c>
+      <c r="C25">
+        <v>1180000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>133</v>
       </c>
       <c r="B26">
-        <v>176000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>134</v>
-      </c>
-      <c r="B27">
         <v>1356000</v>
+      </c>
+      <c r="C26">
+        <v>1180000</v>
       </c>
     </row>
   </sheetData>
@@ -3031,1027 +3230,31 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>153</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="B2">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>155</v>
-      </c>
-      <c r="B2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>157</v>
-      </c>
-      <c r="B3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C3">
-        <v>1356000</v>
-      </c>
-      <c r="D3">
-        <v>1180000</v>
-      </c>
-      <c r="E3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" t="s">
-        <v>159</v>
-      </c>
-      <c r="C4">
-        <v>1206000</v>
-      </c>
-      <c r="D4">
-        <v>1180000</v>
-      </c>
-      <c r="E4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" t="s">
-        <v>161</v>
-      </c>
-      <c r="C5">
-        <v>150000</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5" t="s">
-        <v>160</v>
-      </c>
-      <c r="F5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>162</v>
-      </c>
-      <c r="B6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6">
-        <v>100000</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" t="s">
-        <v>163</v>
-      </c>
-      <c r="C7">
-        <v>100000</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7" t="s">
-        <v>160</v>
-      </c>
-      <c r="F7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>164</v>
-      </c>
-      <c r="B8" t="s">
-        <v>165</v>
-      </c>
-      <c r="C8">
-        <v>270000</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" t="s">
-        <v>166</v>
-      </c>
-      <c r="C9">
-        <v>300000</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9" t="s">
-        <v>160</v>
-      </c>
-      <c r="F9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" t="s">
-        <v>167</v>
-      </c>
-      <c r="C10">
-        <v>-30000</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10" t="s">
-        <v>160</v>
-      </c>
-      <c r="F10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>168</v>
-      </c>
-      <c r="B11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11" t="s">
-        <v>28</v>
-      </c>
-      <c r="F11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" t="s">
-        <v>169</v>
-      </c>
-      <c r="C12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" t="s">
-        <v>170</v>
-      </c>
-      <c r="F12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>171</v>
-      </c>
-      <c r="B13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13">
-        <v>200000</v>
-      </c>
-      <c r="D13">
-        <v>150000</v>
-      </c>
-      <c r="E13" t="s">
-        <v>28</v>
-      </c>
-      <c r="F13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" t="s">
-        <v>172</v>
-      </c>
-      <c r="C14">
-        <v>200000</v>
-      </c>
-      <c r="D14">
-        <v>150000</v>
-      </c>
-      <c r="E14" t="s">
-        <v>160</v>
-      </c>
-      <c r="F14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>173</v>
-      </c>
-      <c r="B15" t="s">
-        <v>174</v>
-      </c>
-      <c r="C15">
-        <v>216000</v>
-      </c>
-      <c r="D15" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" t="s">
-        <v>28</v>
-      </c>
-      <c r="F15" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>28</v>
-      </c>
-      <c r="B16" t="s">
-        <v>175</v>
-      </c>
-      <c r="C16">
-        <v>240000</v>
-      </c>
-      <c r="D16" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" t="s">
-        <v>160</v>
-      </c>
-      <c r="F16" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17" t="s">
-        <v>176</v>
-      </c>
-      <c r="C17">
-        <v>-24000</v>
-      </c>
-      <c r="D17" t="s">
-        <v>28</v>
-      </c>
-      <c r="E17" t="s">
-        <v>160</v>
-      </c>
-      <c r="F17" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>177</v>
-      </c>
-      <c r="B18" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18" t="s">
-        <v>28</v>
-      </c>
-      <c r="F18" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" t="s">
-        <v>169</v>
-      </c>
-      <c r="C19" t="s">
-        <v>28</v>
-      </c>
-      <c r="D19" t="s">
-        <v>28</v>
-      </c>
-      <c r="E19" t="s">
-        <v>170</v>
-      </c>
-      <c r="F19" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>178</v>
-      </c>
-      <c r="B20" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20">
-        <v>220000</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20" t="s">
-        <v>28</v>
-      </c>
-      <c r="F20" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" t="s">
-        <v>179</v>
-      </c>
-      <c r="C21">
-        <v>220000</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21" t="s">
-        <v>160</v>
-      </c>
-      <c r="F21" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>180</v>
-      </c>
-      <c r="B22" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22">
-        <v>240000</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22" t="s">
-        <v>28</v>
-      </c>
-      <c r="F22" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" t="s">
-        <v>181</v>
-      </c>
-      <c r="C23">
-        <v>240000</v>
-      </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-      <c r="E23" t="s">
-        <v>160</v>
-      </c>
-      <c r="F23" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>182</v>
-      </c>
-      <c r="B24" t="s">
-        <v>28</v>
-      </c>
-      <c r="C24">
-        <v>50000</v>
-      </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
-      <c r="E24" t="s">
-        <v>28</v>
-      </c>
-      <c r="F24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>28</v>
-      </c>
-      <c r="B25" t="s">
-        <v>183</v>
-      </c>
-      <c r="C25">
-        <v>50000</v>
-      </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
-      <c r="E25" t="s">
-        <v>160</v>
-      </c>
-      <c r="F25" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>184</v>
-      </c>
-      <c r="B26" t="s">
-        <v>28</v>
-      </c>
-      <c r="C26">
-        <v>96000</v>
-      </c>
-      <c r="D26">
-        <v>66000</v>
-      </c>
-      <c r="E26" t="s">
-        <v>28</v>
-      </c>
-      <c r="F26" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" t="s">
-        <v>185</v>
-      </c>
-      <c r="C27">
-        <v>96000</v>
-      </c>
-      <c r="D27">
-        <v>66000</v>
-      </c>
-      <c r="E27" t="s">
-        <v>160</v>
-      </c>
-      <c r="F27" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>186</v>
-      </c>
-      <c r="B28" t="s">
-        <v>28</v>
-      </c>
-      <c r="C28" t="s">
-        <v>28</v>
-      </c>
-      <c r="D28">
-        <v>0</v>
-      </c>
-      <c r="E28" t="s">
-        <v>28</v>
-      </c>
-      <c r="F28" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>28</v>
-      </c>
-      <c r="B29" t="s">
-        <v>169</v>
-      </c>
-      <c r="C29" t="s">
-        <v>28</v>
-      </c>
-      <c r="D29" t="s">
-        <v>28</v>
-      </c>
-      <c r="E29" t="s">
-        <v>170</v>
-      </c>
-      <c r="F29" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>187</v>
-      </c>
-      <c r="B30" t="s">
-        <v>28</v>
-      </c>
-      <c r="C30">
-        <v>1504000</v>
-      </c>
-      <c r="D30">
-        <v>1264000</v>
-      </c>
-      <c r="E30" t="s">
-        <v>28</v>
-      </c>
-      <c r="F30" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>28</v>
-      </c>
-      <c r="B31" t="s">
-        <v>188</v>
-      </c>
-      <c r="C31">
-        <v>264000</v>
-      </c>
-      <c r="D31">
-        <v>264000</v>
-      </c>
-      <c r="E31" t="s">
-        <v>160</v>
-      </c>
-      <c r="F31" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>28</v>
-      </c>
-      <c r="B32" t="s">
-        <v>189</v>
-      </c>
-      <c r="C32">
-        <v>1300000</v>
-      </c>
-      <c r="D32">
-        <v>1000000</v>
-      </c>
-      <c r="E32" t="s">
-        <v>160</v>
-      </c>
-      <c r="F32" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>28</v>
-      </c>
-      <c r="B33" t="s">
-        <v>190</v>
-      </c>
-      <c r="C33">
-        <v>90000</v>
-      </c>
-      <c r="D33">
-        <v>0</v>
-      </c>
-      <c r="E33" t="s">
-        <v>160</v>
-      </c>
-      <c r="F33" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>28</v>
-      </c>
-      <c r="B34" t="s">
-        <v>191</v>
-      </c>
-      <c r="C34">
-        <v>10000</v>
-      </c>
-      <c r="D34">
-        <v>0</v>
-      </c>
-      <c r="E34" t="s">
-        <v>160</v>
-      </c>
-      <c r="F34" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>28</v>
-      </c>
-      <c r="B35" t="s">
-        <v>192</v>
-      </c>
-      <c r="C35">
-        <v>-160000</v>
-      </c>
-      <c r="D35">
-        <v>0</v>
-      </c>
-      <c r="E35" t="s">
-        <v>160</v>
-      </c>
-      <c r="F35" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>193</v>
-      </c>
-      <c r="B36" t="s">
-        <v>194</v>
-      </c>
-      <c r="C36">
-        <v>-34000</v>
-      </c>
-      <c r="D36">
-        <v>0</v>
-      </c>
-      <c r="E36" t="s">
-        <v>28</v>
-      </c>
-      <c r="F36" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>28</v>
-      </c>
-      <c r="B37" t="s">
-        <v>195</v>
-      </c>
-      <c r="C37">
-        <v>30000</v>
-      </c>
-      <c r="D37" t="s">
-        <v>28</v>
-      </c>
-      <c r="E37" t="s">
-        <v>160</v>
-      </c>
-      <c r="F37" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>28</v>
-      </c>
-      <c r="B38" t="s">
-        <v>196</v>
-      </c>
-      <c r="C38">
-        <v>-24000</v>
-      </c>
-      <c r="D38" t="s">
-        <v>28</v>
-      </c>
-      <c r="E38" t="s">
-        <v>160</v>
-      </c>
-      <c r="F38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>28</v>
-      </c>
-      <c r="B39" t="s">
-        <v>197</v>
-      </c>
-      <c r="C39">
-        <v>-40000</v>
-      </c>
-      <c r="D39" t="s">
-        <v>28</v>
-      </c>
-      <c r="E39" t="s">
-        <v>160</v>
-      </c>
-      <c r="F39" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>198</v>
-      </c>
-      <c r="B40" t="s">
-        <v>199</v>
-      </c>
-      <c r="C40" t="s">
-        <v>28</v>
-      </c>
-      <c r="D40" t="s">
-        <v>28</v>
-      </c>
-      <c r="E40" t="s">
-        <v>28</v>
-      </c>
-      <c r="F40" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>28</v>
-      </c>
-      <c r="B41" t="s">
-        <v>200</v>
-      </c>
-      <c r="C41" t="s">
-        <v>28</v>
-      </c>
-      <c r="D41" t="s">
-        <v>28</v>
-      </c>
-      <c r="E41" t="s">
-        <v>201</v>
-      </c>
-      <c r="F41" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>202</v>
-      </c>
-      <c r="B42" t="s">
-        <v>199</v>
-      </c>
-      <c r="C42" t="s">
-        <v>28</v>
-      </c>
-      <c r="D42" t="s">
-        <v>28</v>
-      </c>
-      <c r="E42" t="s">
-        <v>28</v>
-      </c>
-      <c r="F42" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>28</v>
-      </c>
-      <c r="B43" t="s">
-        <v>200</v>
-      </c>
-      <c r="C43" t="s">
-        <v>28</v>
-      </c>
-      <c r="D43" t="s">
-        <v>28</v>
-      </c>
-      <c r="E43" t="s">
-        <v>201</v>
-      </c>
-      <c r="F43" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>203</v>
-      </c>
-      <c r="B44" t="s">
-        <v>199</v>
-      </c>
-      <c r="C44" t="s">
-        <v>28</v>
-      </c>
-      <c r="D44" t="s">
-        <v>28</v>
-      </c>
-      <c r="E44" t="s">
-        <v>28</v>
-      </c>
-      <c r="F44" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>28</v>
-      </c>
-      <c r="B45" t="s">
-        <v>200</v>
-      </c>
-      <c r="C45" t="s">
-        <v>28</v>
-      </c>
-      <c r="D45" t="s">
-        <v>28</v>
-      </c>
-      <c r="E45" t="s">
-        <v>201</v>
-      </c>
-      <c r="F45" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>204</v>
-      </c>
-      <c r="B46" t="s">
-        <v>199</v>
-      </c>
-      <c r="C46" t="s">
-        <v>28</v>
-      </c>
-      <c r="D46" t="s">
-        <v>28</v>
-      </c>
-      <c r="E46" t="s">
-        <v>28</v>
-      </c>
-      <c r="F46" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>28</v>
-      </c>
-      <c r="B47" t="s">
-        <v>200</v>
-      </c>
-      <c r="C47" t="s">
-        <v>28</v>
-      </c>
-      <c r="D47" t="s">
-        <v>28</v>
-      </c>
-      <c r="E47" t="s">
-        <v>201</v>
-      </c>
-      <c r="F47" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>205</v>
-      </c>
-      <c r="B48" t="s">
-        <v>199</v>
-      </c>
-      <c r="C48" t="s">
-        <v>28</v>
-      </c>
-      <c r="D48" t="s">
-        <v>28</v>
-      </c>
-      <c r="E48" t="s">
-        <v>28</v>
-      </c>
-      <c r="F48" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>28</v>
-      </c>
-      <c r="B49" t="s">
-        <v>200</v>
-      </c>
-      <c r="C49" t="s">
-        <v>28</v>
-      </c>
-      <c r="D49" t="s">
-        <v>28</v>
-      </c>
-      <c r="E49" t="s">
-        <v>201</v>
-      </c>
-      <c r="F49" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>206</v>
-      </c>
-      <c r="B50" t="s">
-        <v>199</v>
-      </c>
-      <c r="C50" t="s">
-        <v>28</v>
-      </c>
-      <c r="D50" t="s">
-        <v>28</v>
-      </c>
-      <c r="E50" t="s">
-        <v>28</v>
-      </c>
-      <c r="F50" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>28</v>
-      </c>
-      <c r="B51" t="s">
-        <v>200</v>
-      </c>
-      <c r="C51" t="s">
-        <v>28</v>
-      </c>
-      <c r="D51" t="s">
-        <v>28</v>
-      </c>
-      <c r="E51" t="s">
-        <v>201</v>
-      </c>
-      <c r="F51" t="s">
-        <v>28</v>
+      <c r="B3">
+        <v>40000</v>
       </c>
     </row>
   </sheetData>
@@ -4062,148 +3265,1027 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>207</v>
+        <v>155</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>208</v>
+        <v>47</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>210</v>
+        <v>13</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>211</v>
+        <v>156</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>212</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B2">
-        <v>150000</v>
-      </c>
-      <c r="C2">
-        <v>150000</v>
-      </c>
-      <c r="F2">
-        <v>120000</v>
+        <v>158</v>
+      </c>
+      <c r="B2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>214</v>
-      </c>
-      <c r="B3">
-        <v>30000</v>
+        <v>160</v>
+      </c>
+      <c r="B3" t="s">
+        <v>161</v>
       </c>
       <c r="C3">
-        <v>30000</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
+        <v>1356000</v>
+      </c>
+      <c r="D3">
+        <v>1180000</v>
+      </c>
+      <c r="E3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>215</v>
-      </c>
-      <c r="B4">
-        <v>24000</v>
+        <v>28</v>
+      </c>
+      <c r="B4" t="s">
+        <v>162</v>
       </c>
       <c r="C4">
-        <v>24000</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
+        <v>1206000</v>
+      </c>
+      <c r="D4">
+        <v>1180000</v>
+      </c>
+      <c r="E4" t="s">
+        <v>163</v>
+      </c>
+      <c r="F4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>216</v>
-      </c>
-      <c r="B5">
-        <v>90000</v>
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>164</v>
       </c>
       <c r="C5">
-        <v>54000</v>
+        <v>150000</v>
       </c>
       <c r="D5">
-        <v>36000</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>163</v>
+      </c>
+      <c r="F5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>217</v>
-      </c>
-      <c r="B6">
-        <v>60000</v>
+        <v>165</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6">
+        <v>100000</v>
       </c>
       <c r="D6">
-        <v>60000</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>196</v>
-      </c>
-      <c r="B7">
-        <v>24000</v>
-      </c>
-      <c r="E7">
-        <v>24000</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
+        <v>28</v>
+      </c>
+      <c r="B7" t="s">
+        <v>166</v>
+      </c>
+      <c r="C7">
+        <v>100000</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>163</v>
+      </c>
+      <c r="F7" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>197</v>
-      </c>
-      <c r="B8">
-        <v>40000</v>
-      </c>
-      <c r="E8">
-        <v>40000</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
+        <v>167</v>
+      </c>
+      <c r="B8" t="s">
+        <v>168</v>
+      </c>
+      <c r="C8">
+        <v>270000</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C9">
+        <v>300000</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9" t="s">
+        <v>163</v>
+      </c>
+      <c r="F9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" t="s">
+        <v>170</v>
+      </c>
+      <c r="C10">
+        <v>-30000</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10" t="s">
+        <v>163</v>
+      </c>
+      <c r="F10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>171</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" t="s">
+        <v>172</v>
+      </c>
+      <c r="C12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" t="s">
+        <v>173</v>
+      </c>
+      <c r="F12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>174</v>
+      </c>
+      <c r="B13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13">
+        <v>200000</v>
+      </c>
+      <c r="D13">
+        <v>150000</v>
+      </c>
+      <c r="E13" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" t="s">
+        <v>175</v>
+      </c>
+      <c r="C14">
+        <v>200000</v>
+      </c>
+      <c r="D14">
+        <v>150000</v>
+      </c>
+      <c r="E14" t="s">
+        <v>163</v>
+      </c>
+      <c r="F14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>176</v>
+      </c>
+      <c r="B15" t="s">
+        <v>177</v>
+      </c>
+      <c r="C15">
+        <v>216000</v>
+      </c>
+      <c r="D15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" t="s">
+        <v>178</v>
+      </c>
+      <c r="C16">
+        <v>240000</v>
+      </c>
+      <c r="D16" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" t="s">
+        <v>163</v>
+      </c>
+      <c r="F16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" t="s">
+        <v>179</v>
+      </c>
+      <c r="C17">
+        <v>-24000</v>
+      </c>
+      <c r="D17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" t="s">
+        <v>163</v>
+      </c>
+      <c r="F17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>180</v>
+      </c>
+      <c r="B18" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" t="s">
+        <v>172</v>
+      </c>
+      <c r="C19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19" t="s">
+        <v>173</v>
+      </c>
+      <c r="F19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>181</v>
+      </c>
+      <c r="B20" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20">
+        <v>220000</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20" t="s">
+        <v>28</v>
+      </c>
+      <c r="F20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" t="s">
+        <v>182</v>
+      </c>
+      <c r="C21">
+        <v>220000</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21" t="s">
+        <v>163</v>
+      </c>
+      <c r="F21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>183</v>
+      </c>
+      <c r="B22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22">
+        <v>240000</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F22" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" t="s">
+        <v>184</v>
+      </c>
+      <c r="C23">
+        <v>240000</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23" t="s">
+        <v>163</v>
+      </c>
+      <c r="F23" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>185</v>
+      </c>
+      <c r="B24" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24">
+        <v>50000</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24" t="s">
+        <v>28</v>
+      </c>
+      <c r="F24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" t="s">
+        <v>186</v>
+      </c>
+      <c r="C25">
+        <v>50000</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25" t="s">
+        <v>163</v>
+      </c>
+      <c r="F25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>187</v>
+      </c>
+      <c r="B26" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26">
+        <v>96000</v>
+      </c>
+      <c r="D26">
+        <v>66000</v>
+      </c>
+      <c r="E26" t="s">
+        <v>28</v>
+      </c>
+      <c r="F26" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" t="s">
+        <v>188</v>
+      </c>
+      <c r="C27">
+        <v>96000</v>
+      </c>
+      <c r="D27">
+        <v>66000</v>
+      </c>
+      <c r="E27" t="s">
+        <v>163</v>
+      </c>
+      <c r="F27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>189</v>
+      </c>
+      <c r="B28" t="s">
+        <v>28</v>
+      </c>
+      <c r="C28" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28" t="s">
+        <v>28</v>
+      </c>
+      <c r="F28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>172</v>
+      </c>
+      <c r="C29" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" t="s">
+        <v>28</v>
+      </c>
+      <c r="E29" t="s">
+        <v>173</v>
+      </c>
+      <c r="F29" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>190</v>
+      </c>
+      <c r="B30" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30">
+        <v>1504000</v>
+      </c>
+      <c r="D30">
+        <v>1264000</v>
+      </c>
+      <c r="E30" t="s">
+        <v>28</v>
+      </c>
+      <c r="F30" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" t="s">
+        <v>191</v>
+      </c>
+      <c r="C31">
+        <v>264000</v>
+      </c>
+      <c r="D31">
+        <v>264000</v>
+      </c>
+      <c r="E31" t="s">
+        <v>163</v>
+      </c>
+      <c r="F31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" t="s">
+        <v>192</v>
+      </c>
+      <c r="C32">
+        <v>1300000</v>
+      </c>
+      <c r="D32">
+        <v>1000000</v>
+      </c>
+      <c r="E32" t="s">
+        <v>163</v>
+      </c>
+      <c r="F32" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>28</v>
+      </c>
+      <c r="B33" t="s">
+        <v>193</v>
+      </c>
+      <c r="C33">
+        <v>90000</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33" t="s">
+        <v>163</v>
+      </c>
+      <c r="F33" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>28</v>
+      </c>
+      <c r="B34" t="s">
+        <v>194</v>
+      </c>
+      <c r="C34">
+        <v>10000</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34" t="s">
+        <v>163</v>
+      </c>
+      <c r="F34" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>28</v>
+      </c>
+      <c r="B35" t="s">
+        <v>195</v>
+      </c>
+      <c r="C35">
+        <v>-160000</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35" t="s">
+        <v>163</v>
+      </c>
+      <c r="F35" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>196</v>
+      </c>
+      <c r="B36" t="s">
+        <v>197</v>
+      </c>
+      <c r="C36">
+        <v>-34000</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36" t="s">
+        <v>28</v>
+      </c>
+      <c r="F36" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>28</v>
+      </c>
+      <c r="B37" t="s">
+        <v>198</v>
+      </c>
+      <c r="C37">
+        <v>30000</v>
+      </c>
+      <c r="D37" t="s">
+        <v>28</v>
+      </c>
+      <c r="E37" t="s">
+        <v>163</v>
+      </c>
+      <c r="F37" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>28</v>
+      </c>
+      <c r="B38" t="s">
+        <v>199</v>
+      </c>
+      <c r="C38">
+        <v>-24000</v>
+      </c>
+      <c r="D38" t="s">
+        <v>28</v>
+      </c>
+      <c r="E38" t="s">
+        <v>163</v>
+      </c>
+      <c r="F38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>28</v>
+      </c>
+      <c r="B39" t="s">
+        <v>200</v>
+      </c>
+      <c r="C39">
+        <v>-40000</v>
+      </c>
+      <c r="D39" t="s">
+        <v>28</v>
+      </c>
+      <c r="E39" t="s">
+        <v>163</v>
+      </c>
+      <c r="F39" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>201</v>
+      </c>
+      <c r="B40" t="s">
+        <v>202</v>
+      </c>
+      <c r="C40" t="s">
+        <v>28</v>
+      </c>
+      <c r="D40" t="s">
+        <v>28</v>
+      </c>
+      <c r="E40" t="s">
+        <v>28</v>
+      </c>
+      <c r="F40" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>28</v>
+      </c>
+      <c r="B41" t="s">
+        <v>203</v>
+      </c>
+      <c r="C41" t="s">
+        <v>28</v>
+      </c>
+      <c r="D41" t="s">
+        <v>28</v>
+      </c>
+      <c r="E41" t="s">
+        <v>204</v>
+      </c>
+      <c r="F41" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>205</v>
+      </c>
+      <c r="B42" t="s">
+        <v>202</v>
+      </c>
+      <c r="C42" t="s">
+        <v>28</v>
+      </c>
+      <c r="D42" t="s">
+        <v>28</v>
+      </c>
+      <c r="E42" t="s">
+        <v>28</v>
+      </c>
+      <c r="F42" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>28</v>
+      </c>
+      <c r="B43" t="s">
+        <v>203</v>
+      </c>
+      <c r="C43" t="s">
+        <v>28</v>
+      </c>
+      <c r="D43" t="s">
+        <v>28</v>
+      </c>
+      <c r="E43" t="s">
+        <v>204</v>
+      </c>
+      <c r="F43" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>206</v>
+      </c>
+      <c r="B44" t="s">
+        <v>202</v>
+      </c>
+      <c r="C44" t="s">
+        <v>28</v>
+      </c>
+      <c r="D44" t="s">
+        <v>28</v>
+      </c>
+      <c r="E44" t="s">
+        <v>28</v>
+      </c>
+      <c r="F44" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>28</v>
+      </c>
+      <c r="B45" t="s">
+        <v>203</v>
+      </c>
+      <c r="C45" t="s">
+        <v>28</v>
+      </c>
+      <c r="D45" t="s">
+        <v>28</v>
+      </c>
+      <c r="E45" t="s">
+        <v>204</v>
+      </c>
+      <c r="F45" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>207</v>
+      </c>
+      <c r="B46" t="s">
+        <v>202</v>
+      </c>
+      <c r="C46" t="s">
+        <v>28</v>
+      </c>
+      <c r="D46" t="s">
+        <v>28</v>
+      </c>
+      <c r="E46" t="s">
+        <v>28</v>
+      </c>
+      <c r="F46" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>28</v>
+      </c>
+      <c r="B47" t="s">
+        <v>203</v>
+      </c>
+      <c r="C47" t="s">
+        <v>28</v>
+      </c>
+      <c r="D47" t="s">
+        <v>28</v>
+      </c>
+      <c r="E47" t="s">
+        <v>204</v>
+      </c>
+      <c r="F47" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>208</v>
       </c>
-      <c r="B9">
-        <v>418000</v>
-      </c>
-      <c r="C9">
-        <v>258000</v>
-      </c>
-      <c r="D9">
-        <v>96000</v>
-      </c>
-      <c r="E9">
-        <v>64000</v>
-      </c>
-      <c r="F9">
-        <v>120000</v>
+      <c r="B48" t="s">
+        <v>202</v>
+      </c>
+      <c r="C48" t="s">
+        <v>28</v>
+      </c>
+      <c r="D48" t="s">
+        <v>28</v>
+      </c>
+      <c r="E48" t="s">
+        <v>28</v>
+      </c>
+      <c r="F48" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>28</v>
+      </c>
+      <c r="B49" t="s">
+        <v>203</v>
+      </c>
+      <c r="C49" t="s">
+        <v>28</v>
+      </c>
+      <c r="D49" t="s">
+        <v>28</v>
+      </c>
+      <c r="E49" t="s">
+        <v>204</v>
+      </c>
+      <c r="F49" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>209</v>
+      </c>
+      <c r="B50" t="s">
+        <v>202</v>
+      </c>
+      <c r="C50" t="s">
+        <v>28</v>
+      </c>
+      <c r="D50" t="s">
+        <v>28</v>
+      </c>
+      <c r="E50" t="s">
+        <v>28</v>
+      </c>
+      <c r="F50" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>28</v>
+      </c>
+      <c r="B51" t="s">
+        <v>203</v>
+      </c>
+      <c r="C51" t="s">
+        <v>28</v>
+      </c>
+      <c r="D51" t="s">
+        <v>28</v>
+      </c>
+      <c r="E51" t="s">
+        <v>204</v>
+      </c>
+      <c r="F51" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/docs/evidence/phase2f/exports/planilla-completa.xlsx
+++ b/docs/evidence/phase2f/exports/planilla-completa.xlsx
@@ -14,16 +14,17 @@
     <sheet sheetId="8" name="EFE no monetarias" state="visible" r:id="rId11"/>
     <sheet sheetId="9" name="Notas" state="visible" r:id="rId12"/>
     <sheet sheetId="10" name="Gastos por función" state="visible" r:id="rId13"/>
-    <sheet sheetId="11" name="Costo de ventas" state="visible" r:id="rId14"/>
-    <sheet sheetId="12" name="Bienes de uso" state="visible" r:id="rId15"/>
-    <sheet sheetId="13" name="Moneda extranjera" state="visible" r:id="rId16"/>
+    <sheet sheetId="11" name="Gastos (preparación)" state="visible" r:id="rId14"/>
+    <sheet sheetId="12" name="Costo de ventas" state="visible" r:id="rId15"/>
+    <sheet sheetId="13" name="Bienes de uso" state="visible" r:id="rId16"/>
+    <sheet sheetId="14" name="Moneda extranjera" state="visible" r:id="rId17"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="275">
   <si>
     <t>ContaLivre — Estados contables (exportación formal)</t>
   </si>
@@ -688,6 +689,42 @@
     <t>RC.5.06 RC Publicidad</t>
   </si>
   <si>
+    <t>Saldo contable</t>
+  </si>
+  <si>
+    <t>Función</t>
+  </si>
+  <si>
+    <t>Base</t>
+  </si>
+  <si>
+    <t>Valor de la base</t>
+  </si>
+  <si>
+    <t>Porcentaje</t>
+  </si>
+  <si>
+    <t>Importe asignado</t>
+  </si>
+  <si>
+    <t>Regla</t>
+  </si>
+  <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>Asignación estructural</t>
+  </si>
+  <si>
+    <t>Porcentaje manual</t>
+  </si>
+  <si>
+    <t>RULE</t>
+  </si>
+  <si>
+    <t>rc-rule-alquileres</t>
+  </si>
+  <si>
     <t>Existencia inicial</t>
   </si>
   <si>
@@ -757,6 +794,9 @@
     <t>Tipo</t>
   </si>
   <si>
+    <t>Corriente</t>
+  </si>
+  <si>
     <t>Clasificación</t>
   </si>
   <si>
@@ -791,6 +831,21 @@
   </si>
   <si>
     <t>Información insuficiente</t>
+  </si>
+  <si>
+    <t>Total activos en moneda extranjera</t>
+  </si>
+  <si>
+    <t>Total pasivos en moneda extranjera</t>
+  </si>
+  <si>
+    <t>Posición neta en moneda extranjera</t>
+  </si>
+  <si>
+    <t>Diferencias de cambio del ejercicio</t>
+  </si>
+  <si>
+    <t>Ninguna cuenta del plan está mapeada a la nota "Diferencias de cambio", por eso no se informa el resultado por diferencias de cambio del ejercicio. Asigná esa nota a las cuentas correspondientes en Configuración → Plan de cuentas y mapeos.</t>
   </si>
   <si>
     <t>Cantidades y cotizaciones por cuenta: información insuficiente (sin detalle operativo cargado). La medición corresponde al saldo del libro en moneda de curso legal. No se utiliza una cotización automática sin identificación de fuente y fecha.</t>
@@ -1652,125 +1707,295 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>47</v>
+        <v>210</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>152</v>
+        <v>221</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B2">
         <v>150000</v>
       </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D2" t="s">
+        <v>229</v>
+      </c>
+      <c r="E2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2">
+        <v>100</v>
+      </c>
+      <c r="G2">
+        <v>150000</v>
+      </c>
+      <c r="H2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B3">
-        <v>500000</v>
-      </c>
-      <c r="C3">
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>30000</v>
+      </c>
+      <c r="C3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D3" t="s">
+        <v>229</v>
+      </c>
+      <c r="E3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3">
+        <v>100</v>
+      </c>
+      <c r="G3">
+        <v>30000</v>
+      </c>
+      <c r="H3" t="s">
+        <v>163</v>
+      </c>
+      <c r="I3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="B4">
-        <v>650000</v>
-      </c>
-      <c r="C4">
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>24000</v>
+      </c>
+      <c r="C4" t="s">
+        <v>212</v>
+      </c>
+      <c r="D4" t="s">
+        <v>229</v>
+      </c>
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4">
+        <v>100</v>
+      </c>
+      <c r="G4">
+        <v>24000</v>
+      </c>
+      <c r="H4" t="s">
+        <v>163</v>
+      </c>
+      <c r="I4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B5">
-        <v>200000</v>
-      </c>
-      <c r="C5">
-        <v>150000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>90000</v>
+      </c>
+      <c r="C5" t="s">
+        <v>212</v>
+      </c>
+      <c r="D5" t="s">
+        <v>230</v>
+      </c>
+      <c r="E5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5">
+        <v>60</v>
+      </c>
+      <c r="G5">
+        <v>54000</v>
+      </c>
+      <c r="H5" t="s">
+        <v>231</v>
+      </c>
+      <c r="I5" t="s">
+        <v>232</v>
+      </c>
+      <c r="J5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B6">
-        <v>450000</v>
-      </c>
-      <c r="C6">
-        <v>250000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>90000</v>
+      </c>
+      <c r="C6" t="s">
+        <v>213</v>
+      </c>
+      <c r="D6" t="s">
+        <v>230</v>
+      </c>
+      <c r="E6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6">
+        <v>40</v>
+      </c>
+      <c r="G6">
+        <v>36000</v>
+      </c>
+      <c r="H6" t="s">
+        <v>231</v>
+      </c>
+      <c r="I6" t="s">
+        <v>232</v>
+      </c>
+      <c r="J6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="B7">
-        <v>450000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>60000</v>
+      </c>
+      <c r="C7" t="s">
+        <v>213</v>
+      </c>
+      <c r="D7" t="s">
+        <v>229</v>
+      </c>
+      <c r="E7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7">
+        <v>100</v>
+      </c>
+      <c r="G7">
+        <v>60000</v>
+      </c>
+      <c r="H7" t="s">
+        <v>163</v>
+      </c>
+      <c r="I7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>199</v>
+      </c>
+      <c r="B8">
+        <v>24000</v>
+      </c>
+      <c r="C8" t="s">
+        <v>214</v>
+      </c>
+      <c r="D8" t="s">
+        <v>229</v>
+      </c>
+      <c r="E8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8">
+        <v>100</v>
+      </c>
+      <c r="G8">
+        <v>24000</v>
+      </c>
+      <c r="H8" t="s">
+        <v>163</v>
+      </c>
+      <c r="I8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J8" t="s">
         <v>26</v>
       </c>
-      <c r="B8" t="s">
-        <v>227</v>
-      </c>
-      <c r="C8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>200</v>
+      </c>
+      <c r="B9">
+        <v>40000</v>
+      </c>
+      <c r="C9" t="s">
+        <v>214</v>
+      </c>
+      <c r="D9" t="s">
+        <v>229</v>
+      </c>
+      <c r="E9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9">
+        <v>100</v>
+      </c>
+      <c r="G9">
+        <v>40000</v>
+      </c>
+      <c r="H9" t="s">
+        <v>163</v>
+      </c>
+      <c r="I9" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" t="s">
         <v>26</v>
-      </c>
-      <c r="B9" t="s">
-        <v>228</v>
-      </c>
-      <c r="C9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" t="s">
-        <v>229</v>
-      </c>
-      <c r="C10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" t="s">
-        <v>230</v>
-      </c>
-      <c r="C11" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1781,112 +2006,125 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>231</v>
+        <v>47</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>232</v>
+        <v>152</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>233</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B2">
+        <v>150000</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>234</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B3">
+        <v>500000</v>
+      </c>
+      <c r="C3">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>235</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="B4">
+        <v>650000</v>
+      </c>
+      <c r="C4">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>236</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="B5">
+        <v>200000</v>
+      </c>
+      <c r="C5">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>237</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="B6">
+        <v>450000</v>
+      </c>
+      <c r="C6">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>238</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="B7">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
         <v>239</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="C8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" t="s">
         <v>240</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="C9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="C10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" t="s">
         <v>242</v>
       </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>240000</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>240000</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>24000</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>24000</v>
-      </c>
-      <c r="J2">
-        <v>216000</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>211</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>240000</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>240000</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>24000</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>24000</v>
-      </c>
-      <c r="J3">
-        <v>216000</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
+      <c r="C11" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1897,10 +2135,126 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>240000</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>240000</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>24000</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>24000</v>
+      </c>
+      <c r="J2">
+        <v>216000</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>240000</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>240000</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>24000</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>24000</v>
+      </c>
+      <c r="J3">
+        <v>216000</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>210</v>
       </c>
@@ -1908,57 +2262,60 @@
         <v>9</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="L1" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>164</v>
       </c>
       <c r="B2" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="C2" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="D2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E2" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="F2" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="G2" t="s">
-        <v>28</v>
+        <v>268</v>
       </c>
       <c r="H2" t="s">
         <v>28</v>
@@ -1966,19 +2323,140 @@
       <c r="I2" t="s">
         <v>28</v>
       </c>
-      <c r="J2">
+      <c r="J2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2">
         <v>150000</v>
       </c>
-      <c r="K2" t="s">
-        <v>28</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>256</v>
+      <c r="L2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>269</v>
+      </c>
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K4">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>270</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>271</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" t="s">
+        <v>28</v>
+      </c>
+      <c r="J6" t="s">
+        <v>28</v>
+      </c>
+      <c r="K6">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>272</v>
+      </c>
+      <c r="B8" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>274</v>
       </c>
     </row>
   </sheetData>
